--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015F8B78-6FCA-4B80-B513-7D426AE088DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33F8FE33-B89E-4022-A4AA-D409669E569E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3749189-E881-469E-B54E-C9CE57848247}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A66B333B-FD43-4E89-B297-5C7FFB08F16B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F851369A-F5E8-4D76-822C-EBB65A35B3D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00885E2A-5AD3-438A-8E10-C249D205D12B}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33F8FE33-B89E-4022-A4AA-D409669E569E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF44BD1A-9287-4B8A-9450-1BE06E073702}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A66B333B-FD43-4E89-B297-5C7FFB08F16B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B819CEC-E07A-4979-827D-5653A2A31711}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00885E2A-5AD3-438A-8E10-C249D205D12B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{767482BB-FC2F-42B0-BEDE-8F80F97DB355}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF44BD1A-9287-4B8A-9450-1BE06E073702}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54A8C725-5D93-4C9C-8CBD-BF99EAD4D206}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B819CEC-E07A-4979-827D-5653A2A31711}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A356414-7564-42A5-94B3-CB38E4D06123}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{767482BB-FC2F-42B0-BEDE-8F80F97DB355}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B7C274A-4156-4DC2-AC48-8B55D57C64B4}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4889,13 +4889,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54A8C725-5D93-4C9C-8CBD-BF99EAD4D206}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{142C1A85-7E82-4893-8394-F07B997D44EA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A356414-7564-42A5-94B3-CB38E4D06123}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF14AC9A-24D4-4932-A63B-895DA1A67AA8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B7C274A-4156-4DC2-AC48-8B55D57C64B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F96EB686-A614-4573-9933-C8612D55790D}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A311E715-8C77-4C93-A6C0-DE094D78BD7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E430FB9F-5CFE-4036-BD76-86DBCB3063B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F6B710E-6D11-4875-BCB3-0D71484E68C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EABFCC4-AEA9-42F3-B1B5-4DEA852857C3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FC79268-7509-4ECC-94B9-E8B77E8BD840}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{163A6545-B068-45FD-9F69-46E9D78CB701}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E430FB9F-5CFE-4036-BD76-86DBCB3063B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBEA4524-DA3F-425B-8E43-7DDBA3F2DB58}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EABFCC4-AEA9-42F3-B1B5-4DEA852857C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7626A9C9-37AB-4D0A-8389-6D97FE600CC7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{163A6545-B068-45FD-9F69-46E9D78CB701}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DE4CAB-A59A-4361-87BC-372CC3FD7BF8}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -3909,291 +3909,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBEA4524-DA3F-425B-8E43-7DDBA3F2DB58}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7626A9C9-37AB-4D0A-8389-6D97FE600CC7}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89DE4CAB-A59A-4361-87BC-372CC3FD7BF8}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -3909,4 +3909,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF23152D-58D4-4D1F-8709-A9B2A9DB0B34}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F99C1803-C283-47F8-8DEB-03DA8F597F15}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4BF1B1-3694-49AD-9961-FF4D7F1EDE3A}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -3909,291 +3909,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF23152D-58D4-4D1F-8709-A9B2A9DB0B34}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F99C1803-C283-47F8-8DEB-03DA8F597F15}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D4BF1B1-3694-49AD-9961-FF4D7F1EDE3A}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -3909,4 +3909,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB42F881-5699-4F72-BB1D-327557579DE9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD9BD5DA-0A27-4D14-815E-AF4C3DC4D4A6}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29AA1944-218B-4C1F-90C4-0A61996CFCA5}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB42F881-5699-4F72-BB1D-327557579DE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D1CB3B5-46F7-4AC5-A243-E3C493EB8401}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD9BD5DA-0A27-4D14-815E-AF4C3DC4D4A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C0EBF74-02F0-47DF-869A-6C778DC94A31}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29AA1944-218B-4C1F-90C4-0A61996CFCA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E51E5625-0D66-4EAD-95E3-95BCAA1B2BBD}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D1CB3B5-46F7-4AC5-A243-E3C493EB8401}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77E7DED7-6C50-4DFC-9EA6-F283DE8BCF41}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C0EBF74-02F0-47DF-869A-6C778DC94A31}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4D898BA-D461-4A4B-AEC3-6D81FD9EC1D5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E51E5625-0D66-4EAD-95E3-95BCAA1B2BBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E248A9F4-CC46-49D1-8BB9-41D884DA0283}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77E7DED7-6C50-4DFC-9EA6-F283DE8BCF41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F63F4E36-721E-4159-8DC8-65F9F9757CCD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4D898BA-D461-4A4B-AEC3-6D81FD9EC1D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F95982-1B15-444D-B301-31C0ABAAA7C0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E248A9F4-CC46-49D1-8BB9-41D884DA0283}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF53C7A8-DF94-4A2E-B702-540C3C6FB227}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F63F4E36-721E-4159-8DC8-65F9F9757CCD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6544D0FD-010B-49E6-B853-0F643EA53FA8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F95982-1B15-444D-B301-31C0ABAAA7C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDD0361B-03F2-4316-BC6C-9166E74AF5DF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF53C7A8-DF94-4A2E-B702-540C3C6FB227}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16AE183C-89FA-4847-AE40-4DF854BABBB4}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6544D0FD-010B-49E6-B853-0F643EA53FA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{636206C1-B524-45FA-B24D-679CBCC24A5C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDD0361B-03F2-4316-BC6C-9166E74AF5DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{429168D5-1477-4472-9E95-07E7BB5EACAB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16AE183C-89FA-4847-AE40-4DF854BABBB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06F8B10-541A-4D8E-A4AA-AFAA8CEE23BE}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -3909,291 +3909,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{636206C1-B524-45FA-B24D-679CBCC24A5C}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{429168D5-1477-4472-9E95-07E7BB5EACAB}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D06F8B10-541A-4D8E-A4AA-AFAA8CEE23BE}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -3909,4 +3909,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FB1CC34-0B96-496B-AF03-065CF9B7D00F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5463A66-8039-4DD0-827E-A09AD4A55013}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{628217A9-57F7-4179-9211-4A511592104C}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3FB1CC34-0B96-496B-AF03-065CF9B7D00F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ABFB99C-2B05-4413-8D70-4C803AB68025}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5463A66-8039-4DD0-827E-A09AD4A55013}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62423B8D-05E8-49FE-A0AE-321626FF7710}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{628217A9-57F7-4179-9211-4A511592104C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6443632-63D4-41D6-8D2E-0DD9D820316E}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6ABFB99C-2B05-4413-8D70-4C803AB68025}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90DBF422-3FB5-4C2F-9531-ADC996127E4B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62423B8D-05E8-49FE-A0AE-321626FF7710}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8968E6F2-85BF-42A8-A0F8-F69C106B6B59}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6443632-63D4-41D6-8D2E-0DD9D820316E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F09B36C-21A7-4125-8E25-462E3D510B2F}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90DBF422-3FB5-4C2F-9531-ADC996127E4B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89AA6D9E-9A08-4963-AAB7-CC620B96DC4E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8968E6F2-85BF-42A8-A0F8-F69C106B6B59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63D0DD61-D5D6-4CDA-A9CB-083CD9445B8B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F09B36C-21A7-4125-8E25-462E3D510B2F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79DEB0CF-A148-49B8-B3A0-42246AAC16FB}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89AA6D9E-9A08-4963-AAB7-CC620B96DC4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{523DAC09-DEE4-4E18-9C83-0C522971173D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63D0DD61-D5D6-4CDA-A9CB-083CD9445B8B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3342FA8F-356D-4A29-BB8B-47A5A20E24C4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79DEB0CF-A148-49B8-B3A0-42246AAC16FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA20444E-1B0F-4E1E-A280-089D32A2E230}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -4187,13 +4187,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{523DAC09-DEE4-4E18-9C83-0C522971173D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EB5AF1F-E443-48E6-BCA5-98E4A125AEA1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3342FA8F-356D-4A29-BB8B-47A5A20E24C4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB11CF27-CD0E-478D-ACA0-703E9078D81B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA20444E-1B0F-4E1E-A280-089D32A2E230}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8303B2A6-01F2-449F-905C-7666F7F9C00D}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -3909,291 +3909,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EB5AF1F-E443-48E6-BCA5-98E4A125AEA1}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB11CF27-CD0E-478D-ACA0-703E9078D81B}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8303B2A6-01F2-449F-905C-7666F7F9C00D}"/>
 </file>
--- a/____EvoM1_TraitTable/gait.xlsx
+++ b/____EvoM1_TraitTable/gait.xlsx
@@ -3909,4 +3909,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7FAF29E-FA62-436B-BC78-64D26620E658}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4846B20-4C86-4275-B3F2-70865563123C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E327AB16-EAA9-4D11-83BB-F77E21C7BA3A}"/>
 </file>